--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467409</v>
+        <v>121467402</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455924</v>
+        <v>455908</v>
       </c>
       <c r="R2" t="n">
-        <v>7045613</v>
+        <v>7045688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467401</v>
+        <v>121467411</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455807</v>
+        <v>455963</v>
       </c>
       <c r="R4" t="n">
-        <v>7045655</v>
+        <v>7045381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467411</v>
+        <v>121467401</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455963</v>
+        <v>455807</v>
       </c>
       <c r="R5" t="n">
-        <v>7045381</v>
+        <v>7045655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467410</v>
+        <v>121467406</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455987</v>
+        <v>455939</v>
       </c>
       <c r="R6" t="n">
-        <v>7045491</v>
+        <v>7045639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467408</v>
+        <v>121467409</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455923</v>
+        <v>455924</v>
       </c>
       <c r="R7" t="n">
-        <v>7045605</v>
+        <v>7045613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467406</v>
+        <v>121467408</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455939</v>
+        <v>455923</v>
       </c>
       <c r="R8" t="n">
-        <v>7045639</v>
+        <v>7045605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467402</v>
+        <v>121467410</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455908</v>
+        <v>455987</v>
       </c>
       <c r="R9" t="n">
-        <v>7045688</v>
+        <v>7045491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467402</v>
+        <v>121467401</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455908</v>
+        <v>455807</v>
       </c>
       <c r="R2" t="n">
-        <v>7045688</v>
+        <v>7045655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467403</v>
+        <v>121467406</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455908</v>
+        <v>455939</v>
       </c>
       <c r="R3" t="n">
-        <v>7045679</v>
+        <v>7045639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467411</v>
+        <v>121467409</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455963</v>
+        <v>455924</v>
       </c>
       <c r="R4" t="n">
-        <v>7045381</v>
+        <v>7045613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467401</v>
+        <v>121467403</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455807</v>
+        <v>455908</v>
       </c>
       <c r="R5" t="n">
-        <v>7045655</v>
+        <v>7045679</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467406</v>
+        <v>121467402</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455939</v>
+        <v>455908</v>
       </c>
       <c r="R6" t="n">
-        <v>7045639</v>
+        <v>7045688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467409</v>
+        <v>121467410</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455924</v>
+        <v>455987</v>
       </c>
       <c r="R7" t="n">
-        <v>7045613</v>
+        <v>7045491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467408</v>
+        <v>121467411</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455923</v>
+        <v>455963</v>
       </c>
       <c r="R8" t="n">
-        <v>7045605</v>
+        <v>7045381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467410</v>
+        <v>121467408</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455987</v>
+        <v>455923</v>
       </c>
       <c r="R9" t="n">
-        <v>7045491</v>
+        <v>7045605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467401</v>
+        <v>121467402</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455807</v>
+        <v>455908</v>
       </c>
       <c r="R2" t="n">
-        <v>7045655</v>
+        <v>7045688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467406</v>
+        <v>121467411</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455939</v>
+        <v>455963</v>
       </c>
       <c r="R3" t="n">
-        <v>7045639</v>
+        <v>7045381</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467409</v>
+        <v>121467408</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455924</v>
+        <v>455923</v>
       </c>
       <c r="R4" t="n">
-        <v>7045613</v>
+        <v>7045605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467403</v>
+        <v>121467409</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455908</v>
+        <v>455924</v>
       </c>
       <c r="R5" t="n">
-        <v>7045679</v>
+        <v>7045613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467402</v>
+        <v>121467401</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455908</v>
+        <v>455807</v>
       </c>
       <c r="R6" t="n">
-        <v>7045688</v>
+        <v>7045655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467410</v>
+        <v>121467403</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455987</v>
+        <v>455908</v>
       </c>
       <c r="R7" t="n">
-        <v>7045491</v>
+        <v>7045679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467411</v>
+        <v>121467406</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455963</v>
+        <v>455939</v>
       </c>
       <c r="R8" t="n">
-        <v>7045381</v>
+        <v>7045639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467408</v>
+        <v>121467410</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455923</v>
+        <v>455987</v>
       </c>
       <c r="R9" t="n">
-        <v>7045605</v>
+        <v>7045491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467402</v>
+        <v>121467411</v>
       </c>
       <c r="B2" t="n">
         <v>57354</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455908</v>
+        <v>455963</v>
       </c>
       <c r="R2" t="n">
-        <v>7045688</v>
+        <v>7045381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467411</v>
+        <v>121467408</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455963</v>
+        <v>455923</v>
       </c>
       <c r="R3" t="n">
-        <v>7045381</v>
+        <v>7045605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467408</v>
+        <v>121467410</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455923</v>
+        <v>455987</v>
       </c>
       <c r="R4" t="n">
-        <v>7045605</v>
+        <v>7045491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467409</v>
+        <v>121467401</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455924</v>
+        <v>455807</v>
       </c>
       <c r="R5" t="n">
-        <v>7045613</v>
+        <v>7045655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467401</v>
+        <v>121467409</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455807</v>
+        <v>455924</v>
       </c>
       <c r="R6" t="n">
-        <v>7045655</v>
+        <v>7045613</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467403</v>
+        <v>121467406</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455908</v>
+        <v>455939</v>
       </c>
       <c r="R7" t="n">
-        <v>7045679</v>
+        <v>7045639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467406</v>
+        <v>121467403</v>
       </c>
       <c r="B8" t="n">
         <v>57354</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455939</v>
+        <v>455908</v>
       </c>
       <c r="R8" t="n">
-        <v>7045639</v>
+        <v>7045679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467410</v>
+        <v>121467402</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455987</v>
+        <v>455908</v>
       </c>
       <c r="R9" t="n">
-        <v>7045491</v>
+        <v>7045688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467411</v>
+        <v>121467406</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455963</v>
+        <v>455939</v>
       </c>
       <c r="R2" t="n">
-        <v>7045381</v>
+        <v>7045639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467408</v>
+        <v>121467409</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455923</v>
+        <v>455924</v>
       </c>
       <c r="R3" t="n">
-        <v>7045605</v>
+        <v>7045613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>121467410</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467401</v>
+        <v>121467402</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455807</v>
+        <v>455908</v>
       </c>
       <c r="R5" t="n">
-        <v>7045655</v>
+        <v>7045688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467409</v>
+        <v>121467411</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455924</v>
+        <v>455963</v>
       </c>
       <c r="R6" t="n">
-        <v>7045613</v>
+        <v>7045381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467406</v>
+        <v>121467401</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455939</v>
+        <v>455807</v>
       </c>
       <c r="R7" t="n">
-        <v>7045639</v>
+        <v>7045655</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467403</v>
+        <v>121467408</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455908</v>
+        <v>455923</v>
       </c>
       <c r="R8" t="n">
-        <v>7045679</v>
+        <v>7045605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467402</v>
+        <v>121467403</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>455908</v>
       </c>
       <c r="R9" t="n">
-        <v>7045688</v>
+        <v>7045679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467406</v>
+        <v>121467401</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455939</v>
+        <v>455807</v>
       </c>
       <c r="R2" t="n">
-        <v>7045639</v>
+        <v>7045655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467409</v>
+        <v>121467411</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455924</v>
+        <v>455963</v>
       </c>
       <c r="R3" t="n">
-        <v>7045613</v>
+        <v>7045381</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467410</v>
+        <v>121467406</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455987</v>
+        <v>455939</v>
       </c>
       <c r="R4" t="n">
-        <v>7045491</v>
+        <v>7045639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467402</v>
+        <v>121467408</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455908</v>
+        <v>455923</v>
       </c>
       <c r="R5" t="n">
-        <v>7045688</v>
+        <v>7045605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467411</v>
+        <v>121467403</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455963</v>
+        <v>455908</v>
       </c>
       <c r="R6" t="n">
-        <v>7045381</v>
+        <v>7045679</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467401</v>
+        <v>121467410</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455807</v>
+        <v>455987</v>
       </c>
       <c r="R7" t="n">
-        <v>7045655</v>
+        <v>7045491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467408</v>
+        <v>121467409</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455923</v>
+        <v>455924</v>
       </c>
       <c r="R8" t="n">
-        <v>7045605</v>
+        <v>7045613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467403</v>
+        <v>121467402</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>455908</v>
       </c>
       <c r="R9" t="n">
-        <v>7045679</v>
+        <v>7045688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467401</v>
+        <v>121467402</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455807</v>
+        <v>455908</v>
       </c>
       <c r="R2" t="n">
-        <v>7045655</v>
+        <v>7045688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467411</v>
+        <v>121467409</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455963</v>
+        <v>455924</v>
       </c>
       <c r="R3" t="n">
-        <v>7045381</v>
+        <v>7045613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467403</v>
+        <v>121467411</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455908</v>
+        <v>455963</v>
       </c>
       <c r="R6" t="n">
-        <v>7045679</v>
+        <v>7045381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467410</v>
+        <v>121467403</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455987</v>
+        <v>455908</v>
       </c>
       <c r="R7" t="n">
-        <v>7045491</v>
+        <v>7045679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467409</v>
+        <v>121467410</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455924</v>
+        <v>455987</v>
       </c>
       <c r="R8" t="n">
-        <v>7045613</v>
+        <v>7045491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467402</v>
+        <v>121467401</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455908</v>
+        <v>455807</v>
       </c>
       <c r="R9" t="n">
-        <v>7045688</v>
+        <v>7045655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467402</v>
+        <v>121467406</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455908</v>
+        <v>455939</v>
       </c>
       <c r="R2" t="n">
-        <v>7045688</v>
+        <v>7045639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467409</v>
+        <v>121467408</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455924</v>
+        <v>455923</v>
       </c>
       <c r="R3" t="n">
-        <v>7045613</v>
+        <v>7045605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467406</v>
+        <v>121467411</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455939</v>
+        <v>455963</v>
       </c>
       <c r="R4" t="n">
-        <v>7045639</v>
+        <v>7045381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467408</v>
+        <v>121467401</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455923</v>
+        <v>455807</v>
       </c>
       <c r="R5" t="n">
-        <v>7045605</v>
+        <v>7045655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467411</v>
+        <v>121467402</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455963</v>
+        <v>455908</v>
       </c>
       <c r="R6" t="n">
-        <v>7045381</v>
+        <v>7045688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467403</v>
+        <v>121467410</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455908</v>
+        <v>455987</v>
       </c>
       <c r="R7" t="n">
-        <v>7045679</v>
+        <v>7045491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467410</v>
+        <v>121467403</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455987</v>
+        <v>455908</v>
       </c>
       <c r="R8" t="n">
-        <v>7045491</v>
+        <v>7045679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467401</v>
+        <v>121467409</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455807</v>
+        <v>455924</v>
       </c>
       <c r="R9" t="n">
-        <v>7045655</v>
+        <v>7045613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467406</v>
+        <v>121467403</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455939</v>
+        <v>455908</v>
       </c>
       <c r="R2" t="n">
-        <v>7045639</v>
+        <v>7045679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467408</v>
+        <v>121467406</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455923</v>
+        <v>455939</v>
       </c>
       <c r="R3" t="n">
-        <v>7045605</v>
+        <v>7045639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467411</v>
+        <v>121467408</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455963</v>
+        <v>455923</v>
       </c>
       <c r="R4" t="n">
-        <v>7045381</v>
+        <v>7045605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467401</v>
+        <v>121467410</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455807</v>
+        <v>455987</v>
       </c>
       <c r="R5" t="n">
-        <v>7045655</v>
+        <v>7045491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467402</v>
+        <v>121467409</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455908</v>
+        <v>455924</v>
       </c>
       <c r="R6" t="n">
-        <v>7045688</v>
+        <v>7045613</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467410</v>
+        <v>121467402</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455987</v>
+        <v>455908</v>
       </c>
       <c r="R7" t="n">
-        <v>7045491</v>
+        <v>7045688</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467403</v>
+        <v>121467401</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455908</v>
+        <v>455807</v>
       </c>
       <c r="R8" t="n">
-        <v>7045679</v>
+        <v>7045655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467409</v>
+        <v>121467411</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455924</v>
+        <v>455963</v>
       </c>
       <c r="R9" t="n">
-        <v>7045613</v>
+        <v>7045381</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467403</v>
+        <v>121467406</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455908</v>
+        <v>455939</v>
       </c>
       <c r="R2" t="n">
-        <v>7045679</v>
+        <v>7045639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467406</v>
+        <v>121467410</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455939</v>
+        <v>455987</v>
       </c>
       <c r="R3" t="n">
-        <v>7045639</v>
+        <v>7045491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467408</v>
+        <v>121467401</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455923</v>
+        <v>455807</v>
       </c>
       <c r="R4" t="n">
-        <v>7045605</v>
+        <v>7045655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467410</v>
+        <v>121467402</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455987</v>
+        <v>455908</v>
       </c>
       <c r="R5" t="n">
-        <v>7045491</v>
+        <v>7045688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467409</v>
+        <v>121467403</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455924</v>
+        <v>455908</v>
       </c>
       <c r="R6" t="n">
-        <v>7045613</v>
+        <v>7045679</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467402</v>
+        <v>121467409</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455908</v>
+        <v>455924</v>
       </c>
       <c r="R7" t="n">
-        <v>7045688</v>
+        <v>7045613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467401</v>
+        <v>121467411</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455807</v>
+        <v>455963</v>
       </c>
       <c r="R8" t="n">
-        <v>7045655</v>
+        <v>7045381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467411</v>
+        <v>121467408</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455963</v>
+        <v>455923</v>
       </c>
       <c r="R9" t="n">
-        <v>7045381</v>
+        <v>7045605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467406</v>
+        <v>121467410</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455939</v>
+        <v>455987</v>
       </c>
       <c r="R2" t="n">
-        <v>7045639</v>
+        <v>7045491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467410</v>
+        <v>121467406</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455987</v>
+        <v>455939</v>
       </c>
       <c r="R3" t="n">
-        <v>7045491</v>
+        <v>7045639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467410</v>
+        <v>121467406</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455987</v>
+        <v>455939</v>
       </c>
       <c r="R2" t="n">
-        <v>7045491</v>
+        <v>7045639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467406</v>
+        <v>121467410</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455939</v>
+        <v>455987</v>
       </c>
       <c r="R3" t="n">
-        <v>7045639</v>
+        <v>7045491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467408</v>
+        <v>121467403</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455923</v>
+        <v>455908</v>
       </c>
       <c r="R2" t="n">
-        <v>7045605</v>
+        <v>7045679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467402</v>
+        <v>121467410</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455908</v>
+        <v>455987</v>
       </c>
       <c r="R3" t="n">
-        <v>7045688</v>
+        <v>7045491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467403</v>
+        <v>121467409</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455908</v>
+        <v>455924</v>
       </c>
       <c r="R4" t="n">
-        <v>7045679</v>
+        <v>7045613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467410</v>
+        <v>121467408</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455987</v>
+        <v>455923</v>
       </c>
       <c r="R5" t="n">
-        <v>7045491</v>
+        <v>7045605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467409</v>
+        <v>121467411</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455924</v>
+        <v>455963</v>
       </c>
       <c r="R6" t="n">
-        <v>7045613</v>
+        <v>7045381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467406</v>
+        <v>121467401</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455939</v>
+        <v>455807</v>
       </c>
       <c r="R7" t="n">
-        <v>7045639</v>
+        <v>7045655</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467411</v>
+        <v>121467406</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455963</v>
+        <v>455939</v>
       </c>
       <c r="R8" t="n">
-        <v>7045381</v>
+        <v>7045639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467401</v>
+        <v>121467402</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455807</v>
+        <v>455908</v>
       </c>
       <c r="R9" t="n">
-        <v>7045655</v>
+        <v>7045688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467403</v>
+        <v>121467401</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455908</v>
+        <v>455807</v>
       </c>
       <c r="R2" t="n">
-        <v>7045679</v>
+        <v>7045655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467410</v>
+        <v>121467406</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455987</v>
+        <v>455939</v>
       </c>
       <c r="R3" t="n">
-        <v>7045491</v>
+        <v>7045639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467409</v>
+        <v>121467408</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455924</v>
+        <v>455923</v>
       </c>
       <c r="R4" t="n">
-        <v>7045613</v>
+        <v>7045605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467408</v>
+        <v>121467411</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455923</v>
+        <v>455963</v>
       </c>
       <c r="R5" t="n">
-        <v>7045605</v>
+        <v>7045381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467411</v>
+        <v>121467410</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455963</v>
+        <v>455987</v>
       </c>
       <c r="R6" t="n">
-        <v>7045381</v>
+        <v>7045491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467401</v>
+        <v>121467402</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455807</v>
+        <v>455908</v>
       </c>
       <c r="R7" t="n">
-        <v>7045655</v>
+        <v>7045688</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467406</v>
+        <v>121467409</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455939</v>
+        <v>455924</v>
       </c>
       <c r="R8" t="n">
-        <v>7045639</v>
+        <v>7045613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467402</v>
+        <v>121467403</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1467,7 +1467,7 @@
         <v>455908</v>
       </c>
       <c r="R9" t="n">
-        <v>7045688</v>
+        <v>7045679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121467401</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467406</v>
+        <v>121467402</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455939</v>
+        <v>455908</v>
       </c>
       <c r="R3" t="n">
-        <v>7045639</v>
+        <v>7045688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467408</v>
+        <v>121467403</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455923</v>
+        <v>455908</v>
       </c>
       <c r="R4" t="n">
-        <v>7045605</v>
+        <v>7045679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467411</v>
+        <v>121467404</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455963</v>
+        <v>455934</v>
       </c>
       <c r="R5" t="n">
-        <v>7045381</v>
+        <v>7045689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467410</v>
+        <v>121467405</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455987</v>
+        <v>455945</v>
       </c>
       <c r="R6" t="n">
-        <v>7045491</v>
+        <v>7045666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467402</v>
+        <v>121467406</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455908</v>
+        <v>455939</v>
       </c>
       <c r="R7" t="n">
-        <v>7045688</v>
+        <v>7045639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467409</v>
+        <v>121467408</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455924</v>
+        <v>455923</v>
       </c>
       <c r="R8" t="n">
-        <v>7045613</v>
+        <v>7045605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467403</v>
+        <v>121467409</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455908</v>
+        <v>455924</v>
       </c>
       <c r="R9" t="n">
-        <v>7045679</v>
+        <v>7045613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,6 +1488,210 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121467410</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>455987</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7045491</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121467411</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>455963</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7045381</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49385-2024 artfynd.xlsx
+++ b/artfynd/A 49385-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467405</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467406</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467408</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467409</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,8 +1742,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467411</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>